--- a/test-data/testData.xlsx
+++ b/test-data/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation\playwright-senior-ui-framework-complete\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EC608D-0C67-4A1B-B41E-441C89D0793B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6C64C6-22A0-4347-9962-FE67C024E56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -544,5 +544,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>